--- a/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>CRH</t>
   </si>
@@ -656,418 +656,431 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42916</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42735</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42551</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42369</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42185</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10777000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7370000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9416000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11069000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10206000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6756000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8870000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10515000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9654000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6533000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="3">
         <v>10128000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9709000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8862500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29206000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13167000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15372000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12215000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>15285000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8583000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12847000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27449000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11944000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11726300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13125100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>27218300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14241400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16005200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10998600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12428300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6483000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5325000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6060000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6760000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6180000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4919000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5710000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6456000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5979000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4726000</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="3">
         <v>6365000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6079000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5832500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19379000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8867000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10060000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8365000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10130000</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X9" s="3">
         <v>8729000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>18391000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8236000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7398500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8960500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>18189500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9780400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>10894500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7845700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8641600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4294000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2045000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3356000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4309000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4026000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1837000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3160000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4059000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3675000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1807000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>3763000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3630000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3030000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9827000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4300000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5312000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3850000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5155000</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X10" s="3">
         <v>4118000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9058000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3708000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4327900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4164600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9028900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4461000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5110700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3152900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3786700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1100,8 +1113,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,8 +1206,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1284,86 +1301,89 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-308000</v>
+      </c>
+      <c r="E14" s="3">
         <v>36000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-34000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-98000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-3000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>17000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>136000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-120000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-121000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-148000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-11000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-18000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>45500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>25000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>2000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>21000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>12000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>5500</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1376,58 +1396,61 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>548000</v>
+      </c>
+      <c r="E15" s="3">
         <v>576000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>550000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>601000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>528000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>477000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>510000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>467000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>424000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>397000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>446000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>402000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>401000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>376000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>46000</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1468,8 +1491,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1499,192 +1525,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8727000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7373000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7998000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9077000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8285000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6743000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7618000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8611000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7922000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6492000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3">
         <v>8350000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8112000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7641000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25879000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12142000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13873000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11451000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13288000</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X17" s="3">
         <v>12051000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>25003000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11352000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10147400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12452700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>25123300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13581700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>14784500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10776700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>11552600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2050000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1418000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1992000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1921000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1252000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1904000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1732000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>41000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>1778000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1597000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1221500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3327000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1025000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1499000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>764000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1997000</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X18" s="3">
         <v>796000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2446000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>592000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1579000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>672300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2095000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>659700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1220700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>221900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>875700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1717,242 +1750,249 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E20" s="3">
         <v>11000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-26000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>10000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>135000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-25000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>-14000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-222000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-96000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-353000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-246000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-533000</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X20" s="3">
         <v>-79000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-478000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-95000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-131600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-146200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-316200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-203100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-132400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-147900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2607000</v>
+      </c>
+      <c r="E21" s="3">
         <v>562000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1977000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2619000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2450000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>480000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1627000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2396000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2162000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>434000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>446000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2194000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2011000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1603500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4870000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1777000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2014000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1344000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3">
         <v>272000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2233000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1015000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2098100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1110900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2964600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1053500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1685200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>503600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1221900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E22" s="3">
         <v>206000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>220000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>209000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>200000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>181000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>160000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>164000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>156000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>133000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>131000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>73000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>82000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3000</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1993,192 +2033,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2172000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-235000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1283000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1947000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1757000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-156000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>852000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1920000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1739000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>95000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3">
         <v>1734000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1591000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1129000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3102000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>929000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1146000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>518000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1464000</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X23" s="3">
         <v>717000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1968000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>497000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1447400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>526100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1778800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>456600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1088300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>74000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>821700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>661000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-55000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>246000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>428000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>425000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-58000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>143000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>531000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>430000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-19000</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="3">
         <v>416000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>379000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>248500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>650000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>201000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>387000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>112000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>375000</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X24" s="3">
         <v>159000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>467000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>119000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-140000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>142900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>473200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>127900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>323100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>18800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2269,192 +2318,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1511000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-180000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1037000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1519000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1332000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-98000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>709000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1389000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1309000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>114000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="3">
         <v>1318000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1212000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>880500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2452000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>728000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>759000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>406000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1089000</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X26" s="3">
         <v>558000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1501000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>378000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1587400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>383200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1305500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>328700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>765200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>55200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>631500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1479000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-183000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1022000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1496000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1313000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-101000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>699000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1353000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1294000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>112000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="3">
         <v>1300000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1197000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>904000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2451000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>698000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>719000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>403000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1076000</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X27" s="3">
         <v>551000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1497000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>378000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1570600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>373300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1275900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>313000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>760700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>54000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2545,8 +2603,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2587,47 +2648,47 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>11000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>271000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>87000</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>47000</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>42000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>1388000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>1083000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>915100</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>28800</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>88900</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2637,8 +2698,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2729,8 +2793,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2821,192 +2888,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>26000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-10000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-135000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>25000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>14000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>222000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>96000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>353000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>246000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>533000</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X32" s="3">
         <v>79000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>478000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>95000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>131600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>146200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>316200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>203100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>132400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>147900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>54000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1486000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-176000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1025000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1503000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1319000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-94000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>703000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1376000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1297000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>116000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3">
         <v>1306000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1199000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>884000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2722000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>785000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>719000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>403000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1123000</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X33" s="3">
         <v>593000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2885000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1461000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2485700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>402100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1364800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>313000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>760700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>54000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3097,197 +3173,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1486000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-176000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1025000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1503000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1319000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-94000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>703000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1376000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1297000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>116000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3">
         <v>1306000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1199000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>884000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2722000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>785000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>719000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>403000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1123000</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X35" s="3">
         <v>593000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2885000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1461000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2485700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>402100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1364800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>313000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>760700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>54000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42916</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42735</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42551</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42369</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42185</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3320,8 +3405,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3354,100 +3440,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3025000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3240000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4096000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4198000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2876000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3352000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3720000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2978000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3066000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3308000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6341000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P41" s="3">
         <v>4275000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5936000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5783000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6292000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7721000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>14661000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9918000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1592000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9191000</v>
-      </c>
-      <c r="X41" s="3">
-        <v>1848000</v>
       </c>
       <c r="Y41" s="3">
         <v>1848000</v>
       </c>
       <c r="Z41" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="AA41" s="3">
         <v>2530000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2137700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2689000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1564100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2825200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6149600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3829000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3538,652 +3628,676 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7006000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5506000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5452000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7108000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6704000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5493000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5036000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6422000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5893000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4798000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4507000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P43" s="3">
         <v>6450000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4300000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4611000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5335000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4122000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4946000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4253000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6008000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4682000</v>
-      </c>
-      <c r="X43" s="3">
-        <v>5091000</v>
       </c>
       <c r="Y43" s="3">
         <v>5091000</v>
       </c>
       <c r="Z43" s="3">
+        <v>5091000</v>
+      </c>
+      <c r="AA43" s="3">
         <v>4539600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5396200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4373300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5548200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4467800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4211600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3121200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5103000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5058000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5251000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5019000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5051000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4960000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4755000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4644000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4514000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4619000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4291000</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3">
         <v>4276000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4194000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3611000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3193000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3117000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2940000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3080000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3673000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3505000</v>
-      </c>
-      <c r="X44" s="3">
-        <v>3151000</v>
       </c>
       <c r="Y44" s="3">
         <v>3151000</v>
       </c>
       <c r="Z44" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="AA44" s="3">
         <v>3247700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3450200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3227000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3362600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3223500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2978000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2652800</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1900000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>69000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>46000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>230000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>371000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>428000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>626000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1461000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>8000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>134000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>35000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>27000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>17000</v>
-      </c>
-      <c r="X45" s="3">
-        <v>31000</v>
       </c>
       <c r="Y45" s="3">
         <v>31000</v>
       </c>
       <c r="Z45" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1370800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>66500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>25300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>29200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>26900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>25800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>640900</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15752000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16239000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15254000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16852000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15151000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14242000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14083000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14840000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15113000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13709000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16885000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P46" s="3">
         <v>15009000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14833000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14044000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14855000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14977000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>22574000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17258000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11283000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17395000</v>
-      </c>
-      <c r="X46" s="3">
-        <v>10121000</v>
       </c>
       <c r="Y46" s="3">
         <v>10121000</v>
       </c>
       <c r="Z46" s="3">
+        <v>10121000</v>
+      </c>
+      <c r="AA46" s="3">
         <v>11688100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11050500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10314600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10504100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10543300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>13365000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10243800</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>464000</v>
+      </c>
+      <c r="E47" s="3">
         <v>487000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>502000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>743000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>712000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>732000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>737000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>929000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>484000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>609000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>620000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>714000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>649000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>904000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>875000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>964000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1049000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1144000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1575000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1565000</v>
-      </c>
-      <c r="X47" s="3">
-        <v>1299000</v>
       </c>
       <c r="Y47" s="3">
         <v>1299000</v>
       </c>
       <c r="Z47" s="3">
+        <v>1299000</v>
+      </c>
+      <c r="AA47" s="3">
         <v>1709400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1641500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1687600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1688600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1676300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1814700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1686800</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26170000</v>
+      </c>
+      <c r="E48" s="3">
         <v>25931000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26408000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25195000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24312000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23451000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22726000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22611000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20514000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20163000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19133000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P48" s="3">
         <v>19322000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18943000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19502000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19100000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19317000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19099000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>39148000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>38153000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18046000</v>
-      </c>
-      <c r="X48" s="3">
-        <v>15607000</v>
       </c>
       <c r="Y48" s="3">
         <v>15607000</v>
       </c>
       <c r="Z48" s="3">
+        <v>15607000</v>
+      </c>
+      <c r="AA48" s="3">
         <v>15663000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13744200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13933600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14146000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14655400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9181500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8712000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15187000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14548000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15147000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14822000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12912000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12683000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12272000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12011000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11337000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11218000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10199000</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>10399000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10287000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9848000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9468000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9373000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9378000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9475000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9702000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9656000</v>
-      </c>
-      <c r="X49" s="3">
-        <v>8615000</v>
       </c>
       <c r="Y49" s="3">
         <v>8615000</v>
       </c>
       <c r="Z49" s="3">
+        <v>8615000</v>
+      </c>
+      <c r="AA49" s="3">
         <v>8629400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8360200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8521600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8629200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8774000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5177700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4898300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4274,8 +4388,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4366,100 +4483,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>979000</v>
+      </c>
+      <c r="E52" s="3">
         <v>962000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1018000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>915000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>897000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>813000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>795000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>830000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>657000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>634000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>632000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3">
         <v>456000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>607000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>372000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>231000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>313000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>275000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>161000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>166000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>115000</v>
-      </c>
-      <c r="X52" s="3">
-        <v>114000</v>
       </c>
       <c r="Y52" s="3">
         <v>114000</v>
       </c>
       <c r="Z52" s="3">
+        <v>114000</v>
+      </c>
+      <c r="AA52" s="3">
         <v>149500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>200500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>232800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>362400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>262500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>253500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>302800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4550,100 +4673,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58552000</v>
+      </c>
+      <c r="E54" s="3">
         <v>58167000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>58329000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>58527000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>53984000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>51921000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>50613000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>51221000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>48105000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46333000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>47469000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P54" s="3">
         <v>45983000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45319000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44670000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>44529000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>44944000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>52375000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>47612000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>43034000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>46777000</v>
-      </c>
-      <c r="X54" s="3">
-        <v>35756000</v>
       </c>
       <c r="Y54" s="3">
         <v>35756000</v>
       </c>
       <c r="Z54" s="3">
+        <v>35756000</v>
+      </c>
+      <c r="AA54" s="3">
         <v>37839400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34996800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34690200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>35330300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>35911500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>29792500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>25843800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4676,8 +4805,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4710,560 +4840,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3535000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2947000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3263000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3156000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3303000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2777000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3207000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2963000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3363000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2730000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3149000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P57" s="3">
         <v>7448000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2930000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5692000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6198000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4792000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5031000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4916000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5773000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5277000</v>
-      </c>
-      <c r="X57" s="3">
-        <v>5155000</v>
       </c>
       <c r="Y57" s="3">
         <v>5155000</v>
       </c>
       <c r="Z57" s="3">
+        <v>5155000</v>
+      </c>
+      <c r="AA57" s="3">
         <v>5423600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5538000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5286900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5880300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5341800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4145900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3397000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2890000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2843000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1577000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4322000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1418000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1705000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3331000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3549000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3477000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3247000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2152000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>2490000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1751000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>846000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>452000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1553000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6185000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6920000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1571000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7213000</v>
-      </c>
-      <c r="X58" s="3">
-        <v>1356000</v>
       </c>
       <c r="Y58" s="3">
         <v>1356000</v>
       </c>
       <c r="Z58" s="3">
+        <v>1356000</v>
+      </c>
+      <c r="AA58" s="3">
         <v>378000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>463000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>302000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>720300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>848200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>412000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>524700</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1029000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1854000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1341000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1560000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1513000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1770000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1222000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1465000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1274000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1620000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2245000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>1289000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1034000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1043000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1262000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1120000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1125000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1030000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1005000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>976000</v>
-      </c>
-      <c r="X59" s="3">
-        <v>984000</v>
       </c>
       <c r="Y59" s="3">
         <v>984000</v>
       </c>
       <c r="Z59" s="3">
+        <v>984000</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1412700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>898300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>887200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>880800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>955900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>322800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>617400</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9977000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10211000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8754000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11596000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8684000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8712000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10296000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10668000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10548000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9997000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10013000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P60" s="3">
         <v>11227000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8041000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7581000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7912000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7465000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12341000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12866000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8349000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13466000</v>
-      </c>
-      <c r="X60" s="3">
-        <v>7495000</v>
       </c>
       <c r="Y60" s="3">
         <v>7495000</v>
       </c>
       <c r="Z60" s="3">
+        <v>7495000</v>
+      </c>
+      <c r="AA60" s="3">
         <v>7214300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6899200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6476000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7481400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7146000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4880700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4539100</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16923000</v>
+      </c>
+      <c r="E61" s="3">
         <v>17585000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18128000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16331000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16180000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15624000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12233000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11957000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11161000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10945000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10987000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>8727000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9204000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11312000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11995000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10958000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>15108000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10604000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11731000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9959000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>8557000</v>
       </c>
       <c r="Y61" s="3">
         <v>8557000</v>
       </c>
       <c r="Z61" s="3">
+        <v>8557000</v>
+      </c>
+      <c r="AA61" s="3">
         <v>9162900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8838600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8251500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8908600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9497600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7241200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6360900</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2309000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2210000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2137000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2050000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1858000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1906000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2005000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1781000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1715000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1856000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3">
         <v>1470000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1877000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4863000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4550000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6173000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6000000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4507000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4543000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4400000</v>
-      </c>
-      <c r="X62" s="3">
-        <v>3733000</v>
       </c>
       <c r="Y62" s="3">
         <v>3733000</v>
       </c>
       <c r="Z62" s="3">
+        <v>3733000</v>
+      </c>
+      <c r="AA62" s="3">
         <v>3546700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3845600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4104300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4229900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4071700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2946300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2973300</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5354,8 +5503,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5446,8 +5598,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5538,100 +5693,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33017000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33622000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32851000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33898000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30354000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29564000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27763000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28055000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26654000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25591000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25848000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P66" s="3">
         <v>24637000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22279000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>24437000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25152000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>25288000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34091000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28584000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25243000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>28427000</v>
-      </c>
-      <c r="X66" s="3">
-        <v>20279000</v>
       </c>
       <c r="Y66" s="3">
         <v>20279000</v>
       </c>
       <c r="Z66" s="3">
+        <v>20279000</v>
+      </c>
+      <c r="AA66" s="3">
         <v>20505300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20143900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19433500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21220200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21308800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15094000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13897900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5664,8 +5825,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5756,8 +5918,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5848,13 +6013,16 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>1000</v>
@@ -5884,10 +6052,10 @@
         <v>1000</v>
       </c>
       <c r="N70" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="O70" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P70" s="3">
         <v>1000</v>
@@ -5920,10 +6088,10 @@
         <v>1000</v>
       </c>
       <c r="Z70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA70" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA70" s="3">
-        <v>1100</v>
       </c>
       <c r="AB70" s="3">
         <v>1100</v>
@@ -5935,13 +6103,16 @@
         <v>1100</v>
       </c>
       <c r="AE70" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AF70" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6032,100 +6203,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>25738000</v>
+      </c>
+      <c r="E72" s="3">
         <v>24793000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25593000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25068000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>24106000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>23375000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>24036000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23831000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23030000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22346000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22918000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3">
         <v>21712000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>22495000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20215000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19463000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12009000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11501000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11761000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11929000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12083000</v>
-      </c>
-      <c r="X72" s="3">
-        <v>9126000</v>
       </c>
       <c r="Y72" s="3">
         <v>9126000</v>
       </c>
       <c r="Z72" s="3">
+        <v>9126000</v>
+      </c>
+      <c r="AA72" s="3">
         <v>9794500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7499600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7420300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6436900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6776800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6156600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6344400</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6216,8 +6393,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6308,8 +6488,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6400,100 +6583,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24035000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23070000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24003000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23308000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22344000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21118000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21606000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21874000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20725000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20014000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20853000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P76" s="3">
         <v>20694000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22156000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20232000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19376000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19655000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18283000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19027000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17790000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18349000</v>
-      </c>
-      <c r="X76" s="3">
-        <v>15476000</v>
       </c>
       <c r="Y76" s="3">
         <v>15476000</v>
       </c>
       <c r="Z76" s="3">
+        <v>15476000</v>
+      </c>
+      <c r="AA76" s="3">
         <v>17332900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14851800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15255600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14109000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14601600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14697300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11944700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6584,197 +6773,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42916</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42735</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42551</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42369</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42185</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1486000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-176000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1025000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1503000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1319000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-94000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>703000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1376000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1297000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>116000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O81" s="3">
         <v>1306000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1199000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>884000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2722000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>785000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>719000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>403000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1123000</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X81" s="3">
         <v>593000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2885000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1461000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2485700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>402100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1364800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>313000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>760700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>54000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6807,100 +7005,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>528000</v>
+      </c>
+      <c r="E83" s="3">
         <v>477000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>358000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>467000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>424000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>397000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>402000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>401000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>384000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>339500</v>
       </c>
       <c r="N83" s="3">
         <v>339500</v>
       </c>
       <c r="O83" s="3">
+        <v>339500</v>
+      </c>
+      <c r="P83" s="3">
         <v>397500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>309500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1765000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>848000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>868000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>826000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X83" s="3">
         <v>-445000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>265000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>518000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>650700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>584800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1185800</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>596900</v>
       </c>
       <c r="AD83" s="3">
         <v>596900</v>
       </c>
       <c r="AE83" s="3">
+        <v>596900</v>
+      </c>
+      <c r="AF83" s="3">
         <v>429600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6991,8 +7193,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7083,8 +7288,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7175,8 +7383,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7267,8 +7478,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7359,100 +7573,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-616000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2915000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1991000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1378000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-659000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2730000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1486000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1485000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-712000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3">
         <v>1631000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1634000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1589500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4210000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1565000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2930000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1008000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X89" s="3">
         <v>-1940000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>57000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-311000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2677100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-54300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2569300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>77400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2822900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-315800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1747800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7485,100 +7705,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-639000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-601000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-821000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-592000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-655000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-645000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-943000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-505000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-624000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-506000</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O91" s="3">
         <v>-404000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-439000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-463500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-967000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-587000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-482000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-514000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-656000</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X91" s="3">
         <v>486000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-77000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-509000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-635200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-568200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-936600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-457800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-610400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-396700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-260600</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7669,8 +7893,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7761,100 +7988,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>134000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-722000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1340000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2910000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-831000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-964000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1886000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1788000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-521000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2096000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-759000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-478000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1521000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2546000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-519000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-613000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-447000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X94" s="3">
         <v>1026000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1093000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2039500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1085400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-807000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-445400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8485600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>301700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7887,100 +8120,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>521000</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>247000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>249000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>500000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>237000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>238000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>481000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>750000</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>761000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>92500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-906000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-729000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-170000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-537000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>96000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-52000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-358000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-116000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-412000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-386500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-260300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-161600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-275800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-135000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8071,8 +8308,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8163,8 +8403,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8255,280 +8498,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1521000</v>
+      </c>
+      <c r="E100" s="3">
         <v>572000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1723000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2331000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1153000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1141000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-42000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-629000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-339000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-176000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>649000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1555000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-514500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3305000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2368000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4992000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5279000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X100" s="3">
         <v>-544000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-456000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1337000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-311000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>667900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1901700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-859400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2637800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2125800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>610400</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E101" s="3">
         <v>75000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-123000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>65000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>12000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-97000</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3">
         <v>-74000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>24000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>68000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>1000</v>
       </c>
       <c r="N101" s="3">
         <v>1000</v>
       </c>
       <c r="O101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P101" s="3">
         <v>-116500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-297000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-107000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>308000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>30000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X101" s="3">
         <v>-11000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>178000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>8000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-81300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-103000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>63700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-33700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>170200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>132600</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-250000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-814000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-141000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1412000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-476000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-407000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>679000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-866000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>637000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3081000</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>1447000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-375000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-445000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1938000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1429000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2367000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5870000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>525000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-287000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>245200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-574800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-75800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1261100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3052900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2281900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2522500</v>
       </c>
     </row>
